--- a/output/Lines of Effort Tracker - Refined.xlsx
+++ b/output/Lines of Effort Tracker - Refined.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="45">
   <si>
     <t xml:space="preserve">LINES OF EFFORT</t>
   </si>
@@ -68,19 +68,94 @@
     <t xml:space="preserve">LAST UPDATED</t>
   </si>
   <si>
+    <t xml:space="preserve">Critical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NZALC Operating Manual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manual approved, published and in use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finalise critical incident chapter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Core chapters drafted; final review pending.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budget Builder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY26/27 budget model confirmed and issued</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirm FY26/27 figures and lock template.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model working; awaiting final figures.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY Summary Production Process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production process documented as a written SOP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document final production steps.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Process mapped; needs written SOP.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Important</t>
   </si>
   <si>
-    <t xml:space="preserve">Example — replace with a Line of Effort</t>
+    <t xml:space="preserve">Course Nomination &amp; Preparation SOP</t>
   </si>
   <si>
     <t xml:space="preserve">SOP approved and implemented</t>
   </si>
   <si>
-    <t xml:space="preserve">Draft to XO for review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Placeholder row — overwrite with real content</t>
+    <t xml:space="preserve">Review with Dave.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draft complete; with reviewer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assistant Training Coordinator Proposal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proposal endorsed and responsibilities handed over</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepare handover brief.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Case built; handover plan forming.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Storeperson Performance &amp; Workforce Assurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resubmit establishment request.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Early stage; establishment case scoping.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Routine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Training Manager Job Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recommendation submitted for command decision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draft recommendation paper.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queued behind priority items.</t>
   </si>
   <si>
     <t xml:space="preserve">Add new Lines of Effort in the first empty row — the table, dropdowns and formatting extend automatically.  Dates: dd mmm yy.  Stale = not updated in 14 days.</t>
@@ -335,7 +410,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="11">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -362,7 +437,31 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FF8A8781"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9E1B20"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF3F3E3B"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFA87B2A"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -719,23 +818,23 @@
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="n">
         <f aca="false">COUNTA(C11:C400)</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D7" s="5" t="n">
         <f aca="false">COUNTIF(B11:B400,"Critical")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F7" s="5" t="n">
         <f aca="false">COUNTIF(B11:B400,"Important")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" s="5" t="n">
         <f aca="false">COUNTIF(B11:B400,"Routine")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="5" t="n">
         <f aca="true">COUNTIF(H11:H400,"&lt;"&amp;TODAY()-14)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -763,7 +862,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="8" t="s">
         <v>14</v>
       </c>
@@ -774,7 +873,7 @@
         <v>16</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>0.45</v>
+        <v>0.8</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>17</v>
@@ -783,62 +882,144 @@
         <v>18</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>46260</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="8"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="13"/>
-    </row>
-    <row r="13" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="8"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="13"/>
-    </row>
-    <row r="14" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="8"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="13"/>
-    </row>
-    <row r="15" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="8"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="13"/>
-    </row>
-    <row r="16" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="8"/>
-      <c r="C16" s="9"/>
+        <v>46181</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>46181</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>46181</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>46181</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>46181</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="D16" s="10"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="13"/>
-    </row>
-    <row r="17" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="8"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="13"/>
+      <c r="E16" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>46181</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>46181</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="8"/>
@@ -905,25 +1086,25 @@
     </row>
     <row r="27" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="14" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H7">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>$H$7&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11:B400">
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>$B11="Critical"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>$B11="Routine"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11:H400">
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>AND($H11&lt;&gt;"",$H11&lt;TODAY()-14)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -936,7 +1117,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{90B88024-4250-4BF4-B72C-D43ED5EBCE8E}</x14:id>
+          <x14:id>{C04EC47C-9AE9-4F73-8C48-5268DF951B26}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -965,7 +1146,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{90B88024-4250-4BF4-B72C-D43ED5EBCE8E}">
+          <x14:cfRule type="dataBar" id="{C04EC47C-9AE9-4F73-8C48-5268DF951B26}">
             <x14:dataBar minLength="0" maxLength="100" axisPosition="none" gradient="false" border="false">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/output/Lines of Effort Tracker - Refined.xlsx
+++ b/output/Lines of Effort Tracker - Refined.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="93">
   <si>
     <t xml:space="preserve">NZALC HQ - LINES OF EFFORT TRACKER</t>
   </si>
@@ -66,6 +66,18 @@
   </si>
   <si>
     <t xml:space="preserve">Critical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Officer Leadership Training</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foundational leadership intervention for junior officers formally endorsed through AITC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirm direction with the boss, then draft the 1–2 page proposition for early Sep AITC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tight scope — a training requirement, not the NZDF system. HQ ACS ownership. Courtesy comms to Sam/Cat/psych once agreed.</t>
   </si>
   <si>
     <t xml:space="preserve">Combat Mindset Submission</t>
@@ -186,6 +198,42 @@
     <t xml:space="preserve">Early/mid Nov (potential dates)</t>
   </si>
   <si>
+    <t xml:space="preserve">TFCC Course Correction &amp; TF Instructor Transition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erroneous RF course requirement removed and TF instructor delivery in place</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Call Billy Vince to remove the RF course requirement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replace the requirement with the intended leadership outcomes. Instructor transition follows the December TTT. Phone, not email.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpine Touring Resource Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource model decided — reduced internal footprint, contractor support, or course ceased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conduct the resource review with Tony</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Five staff plus significant preparation and gear for one annual course is difficult to justify.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Psychometric &amp; Workforce Continuity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">September staffing decisions confirmed with cover in place</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarify the James option for off-site psychometric administration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responsibilities don't align to national position descriptions. September is the decision point — keep HR engagement moving.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Routine</t>
   </si>
   <si>
@@ -237,16 +285,25 @@
     <t xml:space="preserve">Review completed and reported</t>
   </si>
   <si>
-    <t xml:space="preserve">No update at this stage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not yet started.</t>
+    <t xml:space="preserve">Determine whether the 8–10 day model can become a ~5-day package</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not yet started — progress figure needs correcting.</t>
   </si>
   <si>
     <t xml:space="preserve">Support to HUMINT Platoon FTX</t>
   </si>
   <si>
     <t xml:space="preserve">Support delivered to FTX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Civil Support Session (11 Oct 26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Session delivered with 360-focused instructor support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calendar the session and allocate one — preferably two — instructors</t>
   </si>
 </sst>
 </file>
@@ -643,8 +700,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblLoE" displayName="tblLoE" ref="A7:G28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A7:G28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblLoE" displayName="tblLoE" ref="A7:G33" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A7:G33"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Priority"/>
     <tableColumn id="2" name="Line of Effort"/>
@@ -837,7 +894,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.5"/>
@@ -884,24 +941,24 @@
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="n">
         <f aca="false">COUNTA(B8:B41)</f>
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="5" t="n">
         <f aca="false">COUNTIF(A8:A41,"Critical")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" s="5" t="n">
         <f aca="false">COUNTIF(A8:A41,"Important")</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E5" s="5" t="n">
         <f aca="false">COUNTIF(A8:A41,"Routine")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" s="4" t="n">
         <f aca="true">COUNTIF(G8:G41,"&lt;"&amp;TODAY()-14)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G5" s="4"/>
     </row>
@@ -929,25 +986,27 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="9"/>
+      <c r="C8" s="9" t="s">
+        <v>15</v>
+      </c>
       <c r="D8" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>46244</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -955,81 +1014,85 @@
         <v>13</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="9" t="s">
         <v>18</v>
       </c>
+      <c r="C9" s="9"/>
       <c r="D9" s="10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E9" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>19</v>
+      </c>
       <c r="F9" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G9" s="11" t="n">
         <v>46244</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="9"/>
+        <v>0.6</v>
+      </c>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9" t="s">
+        <v>23</v>
+      </c>
       <c r="G10" s="11" t="n">
         <v>46244</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="9" t="s">
         <v>26</v>
       </c>
+      <c r="F11" s="9"/>
       <c r="G11" s="11" t="n">
         <v>46244</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="9"/>
+      <c r="C12" s="9" t="s">
+        <v>28</v>
+      </c>
       <c r="D12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
+        <v>0.5</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>30</v>
+      </c>
       <c r="G12" s="11" t="n">
-        <v>46204</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1037,7 +1100,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="10" t="n">
@@ -1046,7 +1109,7 @@
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="G13" s="11" t="n">
-        <v>46211</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1054,25 +1117,21 @@
         <v>13</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>30</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="C14" s="9"/>
       <c r="D14" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E14" s="9"/>
-      <c r="F14" s="9" t="s">
-        <v>31</v>
-      </c>
+      <c r="F14" s="9"/>
       <c r="G14" s="11" t="n">
-        <v>46244</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>33</v>
@@ -1081,21 +1140,19 @@
         <v>34</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E15" s="9" t="s">
+        <v>0.5</v>
+      </c>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9" t="s">
         <v>35</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>36</v>
       </c>
       <c r="G15" s="11" t="n">
         <v>46244</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>37</v>
@@ -1104,7 +1161,7 @@
         <v>38</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>39</v>
@@ -1116,20 +1173,24 @@
         <v>46244</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="9"/>
+      <c r="C17" s="9" t="s">
+        <v>42</v>
+      </c>
       <c r="D17" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="9"/>
+        <v>0.7</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>43</v>
+      </c>
       <c r="F17" s="9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G17" s="11" t="n">
         <v>46244</v>
@@ -1137,49 +1198,45 @@
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>44</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C18" s="9"/>
       <c r="D18" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
+      <c r="F18" s="9" t="s">
+        <v>46</v>
+      </c>
       <c r="G18" s="11" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="11" t="n">
         <v>46230</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" s="10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="G19" s="11" t="n">
-        <v>46244</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>49</v>
@@ -1188,7 +1245,7 @@
         <v>50</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>51</v>
@@ -1197,171 +1254,284 @@
         <v>52</v>
       </c>
       <c r="G20" s="11" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G21" s="11" t="n">
         <v>46240</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D21" s="10" t="n">
+    <row r="22" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="11" t="n">
-        <v>46244</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
+      <c r="E22" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>60</v>
+      </c>
       <c r="G22" s="11" t="n">
-        <v>46244</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>46244</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="9"/>
+        <v>0</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>67</v>
+      </c>
       <c r="F24" s="9" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>46205</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
       <c r="G25" s="11" t="n">
-        <v>46230</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>66</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="C26" s="9"/>
       <c r="D26" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E26" s="9"/>
-      <c r="F26" s="9" t="s">
-        <v>67</v>
-      </c>
+      <c r="F26" s="9"/>
       <c r="G26" s="11" t="n">
-        <v>46230</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D27" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>46230</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D28" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G28" s="11" t="n">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D29" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="11" t="n">
         <v>46230</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G30" s="11" t="n">
+        <v>46230</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="G31" s="11" t="n">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="G32" s="11" t="n">
+        <v>46230</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F33" s="9"/>
+      <c r="G33" s="11" t="n">
+        <v>46261</v>
       </c>
     </row>
   </sheetData>
@@ -1402,7 +1572,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{BC89C539-82E6-4034-B97F-7B4F31F76199}</x14:id>
+          <x14:id>{2D93C78C-BF60-4E3A-A2BA-B058DB9082A2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -1431,7 +1601,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{BC89C539-82E6-4034-B97F-7B4F31F76199}">
+          <x14:cfRule type="dataBar" id="{2D93C78C-BF60-4E3A-A2BA-B058DB9082A2}">
             <x14:dataBar minLength="0" maxLength="100" axisPosition="none" gradient="false" border="false">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
